--- a/top10_by_country_asymmetry.xlsx
+++ b/top10_by_country_asymmetry.xlsx
@@ -708,26 +708,26 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>BHIP.BA</t>
+          <t>LONG.BA</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Banco Hipotecario S.A.</t>
+          <t>Longvie S.A.</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
       <c r="H5" s="11" t="n">
-        <v>535499997184</v>
+        <v>9707070464</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -735,16 +735,16 @@
         </is>
       </c>
       <c r="J5" s="13" t="n">
-        <v>0.4018153174543998</v>
+        <v>0.3913422366405466</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>0.3719536002687624</v>
+        <v>0.3506586413338435</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>0.789149</v>
+        <v>0.45</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -763,26 +763,26 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>LONG.BA</t>
+          <t>BHIP.BA</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Longvie S.A.</t>
+          <t>Banco Hipotecario S.A.</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>9707070464</v>
+        <v>535499997184</v>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="J6" s="13" t="n">
-        <v>0.3913422366405466</v>
+        <v>0.3830395611695546</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>0.3506586413338435</v>
+        <v>0.3545732022486955</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>0.45</v>
+        <v>0.702064</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -818,17 +818,17 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>CVH.BA</t>
+          <t>BYMA.BA</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Cablevision Holding S.A.</t>
+          <t>Bolsas y Mercados Argentinos S.A.</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="H7" s="11" t="n">
-        <v>1665524563968</v>
+        <v>2294352445440</v>
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="J7" s="13" t="n">
-        <v>0.3439677358052459</v>
+        <v>0.3771931277056725</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>0.3998479866898475</v>
+        <v>0.3774551911094</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>0.592534</v>
+        <v>0.322729</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -873,17 +873,17 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>BBAR.BA</t>
+          <t>CVH.BA</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Banco BBVA Argentina S.A.</t>
+          <t>Cablevision Holding S.A.</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>5731902816256</v>
+        <v>1665524563968</v>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
@@ -900,16 +900,16 @@
         </is>
       </c>
       <c r="J8" s="13" t="n">
-        <v>0.3364572846165174</v>
+        <v>0.3439677358052459</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>0.3461368913108887</v>
+        <v>0.3998479866898475</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>0.611671</v>
+        <v>0.592534</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -928,17 +928,17 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>RIGO.BA</t>
+          <t>OEST.BA</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Rigolleau S.A.</t>
+          <t>Grupo Concesionario del Oeste S.A.</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="H9" s="11" t="n">
-        <v>67309846528</v>
+        <v>124160000000</v>
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
@@ -955,16 +955,16 @@
         </is>
       </c>
       <c r="J9" s="13" t="n">
-        <v>0.3337730170225293</v>
+        <v>0.3405145261307139</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>0.2958414971266913</v>
+        <v>0.3874484262180857</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0.699673</v>
+        <v>0.652437</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -983,43 +983,43 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>TGNO4.BA</t>
+          <t>RIGO.BA</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Transportadora de Gas del Norte S.A.</t>
+          <t>Rigolleau S.A.</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>1898095443968</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>67309846528</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J10" s="13" t="n">
-        <v>0.3248603723309041</v>
+        <v>0.3337730170225293</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>0.3806097116649281</v>
+        <v>0.2958414971266913</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>0.68327</v>
+        <v>0.699673</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1038,43 +1038,43 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>CECO2.BA</t>
+          <t>BBAR.BA</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Enel Generacion Costanera S.A.</t>
+          <t>Banco BBVA Argentina S.A.</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H11" s="11" t="n">
-        <v>346782236672</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>5731902816256</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J11" s="13" t="n">
-        <v>0.3203783755699272</v>
+        <v>0.3289861948483956</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>0.4095969232373488</v>
+        <v>0.3384508642718555</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>0.741105</v>
+        <v>0.567823</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1093,43 +1093,43 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>GBAN.BA</t>
+          <t>TGNO4.BA</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Naturgy BAN, S.A.</t>
+          <t>Transportadora de Gas del Norte S.A.</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>651079909376</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>1898095443968</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J12" s="13" t="n">
-        <v>0.3181169565010266</v>
+        <v>0.3248603723309041</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>0.3862431384238654</v>
+        <v>0.3806097116649281</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0.720064</v>
+        <v>0.68327</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1148,43 +1148,43 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>CADO.BA</t>
+          <t>CECO2.BA</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Carlos Casado S.A.</t>
+          <t>Enel Generacion Costanera S.A.</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H13" s="11" t="n">
-        <v>70840000512</v>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>346782236672</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J13" s="13" t="n">
-        <v>0.3131404678952449</v>
+        <v>0.3203783755699272</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>0.3479338532169387</v>
+        <v>0.4095969232373488</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>0.396135</v>
+        <v>0.741105</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="J14" s="13" t="n">
-        <v>0.4725691393511089</v>
+        <v>0.5732919298430178</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>0.3375004952202665</v>
+        <v>0.4094349252121699</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>0.313824</v>
+        <v>0.391612</v>
       </c>
       <c r="M14" s="11" t="n">
         <v>3</v>
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="J15" s="13" t="n">
-        <v>0.4679569477074025</v>
+        <v>0.5327871324524621</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>0.3986716631732392</v>
+        <v>0.4539031491096375</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>0.510705</v>
+        <v>0.559733</v>
       </c>
       <c r="M15" s="11" t="n">
         <v>1</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="J18" s="13" t="n">
-        <v>0.4052232684918046</v>
+        <v>0.3956002470055242</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>0.4433745152714897</v>
+        <v>0.4328454987547271</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>0.675305</v>
+        <v>0.578192</v>
       </c>
       <c r="M18" s="11" t="n">
         <v>3</v>
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="J22" s="13" t="n">
-        <v>0.3447037130220343</v>
+        <v>0.3424204577934261</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>0.3145135298803299</v>
+        <v>0.3124302489801286</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>0.34871</v>
+        <v>0.335649</v>
       </c>
       <c r="M22" s="11" t="n">
         <v>0</v>
@@ -1890,13 +1890,13 @@
         </is>
       </c>
       <c r="J26" s="13" t="n">
-        <v>0.5844787751742412</v>
+        <v>0.5888251966660882</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>0.4472755132093951</v>
+        <v>0.4506016355357546</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0.332367</v>
+        <v>0.354426</v>
       </c>
       <c r="M26" s="11" t="n">
         <v>3</v>
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="J29" s="13" t="n">
-        <v>0.545564687399994</v>
+        <v>0.52912758223851</v>
       </c>
       <c r="K29" s="13" t="n">
-        <v>0.3885346164113321</v>
+        <v>0.3768286088629594</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>0.53241</v>
+        <v>0.466233</v>
       </c>
       <c r="M29" s="11" t="n">
         <v>1</v>
@@ -2138,17 +2138,17 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>BRK.AX</t>
+          <t>MCA.AX</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Brookside Energy Limited</t>
+          <t>Murray Cod Australia Limited</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -2157,24 +2157,24 @@
         </is>
       </c>
       <c r="H31" s="11" t="n">
-        <v>44327860</v>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>25237732</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J31" s="13" t="n">
-        <v>0.501366546554772</v>
+        <v>0.5100775989052906</v>
       </c>
       <c r="K31" s="13" t="n">
-        <v>0.4843885758482467</v>
+        <v>0.4568473086443722</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>0.405213</v>
+        <v>0.626341</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -2193,17 +2193,17 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>FWD.AX</t>
+          <t>BRK.AX</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Fleetwood Limited</t>
+          <t>Brookside Energy Limited</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="H32" s="11" t="n">
-        <v>157850768</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>44327860</v>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J32" s="13" t="n">
-        <v>0.4915846785563</v>
+        <v>0.501366546554772</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>0.4635354199538016</v>
+        <v>0.4843885758482467</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>0.976504</v>
+        <v>0.405213</v>
       </c>
       <c r="M32" s="11" t="n">
         <v>3</v>
@@ -2248,26 +2248,26 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>TIA.AX</t>
+          <t>SUN.AX</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Tian An Australia Limited</t>
+          <t>Suncorp Group Limited</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="H33" s="11" t="n">
-        <v>16888722</v>
+        <v>18724509696</v>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
@@ -2275,13 +2275,13 @@
         </is>
       </c>
       <c r="J33" s="13" t="n">
-        <v>0.4548030253099751</v>
+        <v>0.4939354726122924</v>
       </c>
       <c r="K33" s="13" t="n">
-        <v>0.4274494176335735</v>
+        <v>0.4519555696747713</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>0.832579</v>
+        <v>0.627736</v>
       </c>
       <c r="M33" s="11" t="n">
         <v>4</v>
@@ -2578,26 +2578,26 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>IEP.BR</t>
+          <t>AGS.BR</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Iep Invest, NV</t>
+          <t>ageas SA/NV</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="H39" s="11" t="n">
-        <v>44474276</v>
+        <v>14363478016</v>
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
@@ -2605,16 +2605,16 @@
         </is>
       </c>
       <c r="J39" s="13" t="n">
-        <v>0.385419151074934</v>
+        <v>0.3965022673093251</v>
       </c>
       <c r="K39" s="13" t="n">
-        <v>0.3693842065742337</v>
+        <v>0.3013153051633526</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>0.606231</v>
+        <v>0.544967</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2633,26 +2633,26 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>ONTEX.BR</t>
+          <t>IEP.BR</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Ontex Group NV</t>
+          <t>Iep Invest, NV</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
-        <v>212091152</v>
+        <v>44474276</v>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
@@ -2660,16 +2660,16 @@
         </is>
       </c>
       <c r="J40" s="13" t="n">
-        <v>0.3409600577685669</v>
+        <v>0.385419151074934</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>0.3496576496051906</v>
+        <v>0.3693842065742337</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>0.913856</v>
+        <v>0.606231</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2688,26 +2688,26 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>ROU.BR</t>
+          <t>ONTEX.BR</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Roularta Media Group NV</t>
+          <t>Ontex Group NV</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H41" s="11" t="n">
-        <v>160459904</v>
+        <v>212091152</v>
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
@@ -2715,16 +2715,16 @@
         </is>
       </c>
       <c r="J41" s="13" t="n">
-        <v>0.3404707845748069</v>
+        <v>0.3409600577685669</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>0.3771173539268053</v>
+        <v>0.3496576496051906</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>0.72259</v>
+        <v>0.913856</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2743,17 +2743,17 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>MIKO.BR</t>
+          <t>ROU.BR</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Miko NV</t>
+          <t>Roularta Media Group NV</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="H42" s="11" t="n">
-        <v>72036000</v>
+        <v>160459904</v>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="J42" s="13" t="n">
-        <v>0.3403879647690271</v>
+        <v>0.3404707845748069</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>0.405976915615002</v>
+        <v>0.3771173539268053</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>0.737615</v>
+        <v>0.72259</v>
       </c>
       <c r="M42" s="11" t="n">
         <v>1</v>
@@ -2798,26 +2798,26 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>WEHB.BR</t>
+          <t>MIKO.BR</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Wereldhave Belgium Naamloze vennootschap</t>
+          <t>Miko NV</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H43" s="11" t="n">
-        <v>596862016</v>
+        <v>72036000</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2825,16 +2825,16 @@
         </is>
       </c>
       <c r="J43" s="13" t="n">
-        <v>0.3250485804316758</v>
+        <v>0.3403879647690271</v>
       </c>
       <c r="K43" s="13" t="n">
-        <v>0.4027906246594216</v>
+        <v>0.405976915615002</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>0.641494</v>
+        <v>0.737615</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>BGIP4.SA</t>
+          <t>IRBR3.SA</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Banco do Estado de Sergipe S.A.</t>
+          <t>IRB-Brasil Resseguros S.A.</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
@@ -2868,28 +2868,28 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H44" s="11" t="n">
-        <v>746694272</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>4279219200</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="J44" s="13" t="n">
-        <v>0.555729837694053</v>
+        <v>0.5693286568729902</v>
       </c>
       <c r="K44" s="13" t="n">
-        <v>0.4843279603345583</v>
+        <v>0.4559465926974371</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>0.82196</v>
+        <v>0.538142</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2908,26 +2908,26 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>ENJU3.SA</t>
+          <t>BGIP4.SA</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Enjoei.com.br Atividades de Internet S.A.</t>
+          <t>Banco do Estado de Sergipe S.A.</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H45" s="11" t="n">
-        <v>217319056</v>
+        <v>746694272</v>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
@@ -2935,16 +2935,16 @@
         </is>
       </c>
       <c r="J45" s="13" t="n">
-        <v>0.5331474597294283</v>
+        <v>0.5507670961041651</v>
       </c>
       <c r="K45" s="13" t="n">
-        <v>0.4432476522180012</v>
+        <v>0.4800028470351332</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>0.571504</v>
+        <v>0.787203</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -2963,43 +2963,43 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>NGRD3.SA</t>
+          <t>ENJU3.SA</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Neogrid Participacoes S.A.</t>
+          <t>Enjoei.com.br Atividades de Internet S.A.</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
       <c r="H46" s="11" t="n">
-        <v>290239584</v>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>217319056</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J46" s="13" t="n">
-        <v>0.5159536357644642</v>
+        <v>0.5331474597294283</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>0.4106642900582641</v>
+        <v>0.4432476522180012</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>0.54189</v>
+        <v>0.571504</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3018,43 +3018,43 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>IRBR3.SA</t>
+          <t>NGRD3.SA</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>IRB-Brasil Resseguros S.A.</t>
+          <t>Neogrid Participacoes S.A.</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H47" s="11" t="n">
-        <v>4279219200</v>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>290239584</v>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J47" s="13" t="n">
-        <v>0.5133395767222523</v>
+        <v>0.5159536357644642</v>
       </c>
       <c r="K47" s="13" t="n">
-        <v>0.4111077636400626</v>
+        <v>0.4106642900582641</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>0.515798</v>
+        <v>0.54189</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3100,13 +3100,13 @@
         </is>
       </c>
       <c r="J48" s="13" t="n">
-        <v>0.4904841362179138</v>
+        <v>0.4821967154909055</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>0.4616827626999726</v>
+        <v>0.4538819817686964</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>0.753015</v>
+        <v>0.703759</v>
       </c>
       <c r="M48" s="11" t="n">
         <v>3</v>
@@ -3128,12 +3128,12 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>SANB4.SA</t>
+          <t>RBVA11.SA</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Banco Santander (Brasil) S.A.</t>
+          <t>Fundo Invest Imobiliario Agencias Caixa - FII Fund</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
@@ -3143,25 +3143,25 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
       <c r="H49" s="11" t="n">
-        <v>106695892992</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>26925068</v>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="J49" s="13" t="n">
-        <v>0.4832519303594071</v>
+        <v>0.4809753781401246</v>
       </c>
       <c r="K49" s="13" t="n">
-        <v>0.4595819147687425</v>
+        <v>0.3989981421013386</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>0.757193</v>
+        <v>0.568893</v>
       </c>
       <c r="M49" s="11" t="n">
         <v>3</v>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>RBVA11.SA</t>
+          <t>SANB4.SA</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Fundo Invest Imobiliario Agencias Caixa - FII Fund</t>
+          <t>Banco Santander (Brasil) S.A.</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
@@ -3198,25 +3198,25 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="H50" s="11" t="n">
-        <v>26925068</v>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>106695892992</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="J50" s="13" t="n">
-        <v>0.4809753781401246</v>
+        <v>0.4748868500035161</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>0.3989981421013386</v>
+        <v>0.4516265618655569</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>0.568893</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="M50" s="11" t="n">
         <v>3</v>

--- a/top10_by_country_asymmetry.xlsx
+++ b/top10_by_country_asymmetry.xlsx
@@ -29,33 +29,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <color rgb="00404040"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <color rgb="00707070"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <i val="1"/>
       <color rgb="00707070"/>
       <sz val="10"/>
